--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_18-05-2026.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_18-05-2026.xlsx
@@ -839,7 +839,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>£23.23</t>
+          <t>POA</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -2587,7 +2587,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>£118.47</t>
+          <t>POA</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
